--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/ILLINOIS_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/ILLINOIS_2021.xlsx
@@ -931,7 +931,7 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="33">
@@ -1201,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="D47">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="48">
@@ -1615,7 +1615,7 @@
         <v>6</v>
       </c>
       <c r="D70">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="71">
@@ -1669,7 +1669,7 @@
         <v>6</v>
       </c>
       <c r="D73">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="74">
@@ -1867,7 +1867,7 @@
         <v>6</v>
       </c>
       <c r="D84">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="85">
@@ -2029,7 +2029,7 @@
         <v>6</v>
       </c>
       <c r="D93">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="94">
@@ -2227,7 +2227,7 @@
         <v>6</v>
       </c>
       <c r="D104">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="105">
@@ -2335,7 +2335,7 @@
         <v>6</v>
       </c>
       <c r="D110">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="111">
@@ -2947,7 +2947,7 @@
         <v>6</v>
       </c>
       <c r="D144">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="145">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C149">
@@ -3433,7 +3433,7 @@
         <v>6</v>
       </c>
       <c r="D171">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="172">
@@ -3667,7 +3667,7 @@
         <v>579</v>
       </c>
       <c r="D184">
-        <v>0.009264148226371623</v>
+        <v>0.009264148226371624</v>
       </c>
     </row>
     <row r="185">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C204">
@@ -4153,7 +4153,7 @@
         <v>6</v>
       </c>
       <c r="D211">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="212">
@@ -4171,7 +4171,7 @@
         <v>6</v>
       </c>
       <c r="D212">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="213">
@@ -4603,7 +4603,7 @@
         <v>6</v>
       </c>
       <c r="D236">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="237">
@@ -4909,7 +4909,7 @@
         <v>6</v>
       </c>
       <c r="D253">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="254">
@@ -5125,7 +5125,7 @@
         <v>6</v>
       </c>
       <c r="D265">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="266">
@@ -5431,7 +5431,7 @@
         <v>6</v>
       </c>
       <c r="D282">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="283">
@@ -5485,7 +5485,7 @@
         <v>6</v>
       </c>
       <c r="D285">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="286">
@@ -5773,7 +5773,7 @@
         <v>6</v>
       </c>
       <c r="D301">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="302">
@@ -6061,7 +6061,7 @@
         <v>6</v>
       </c>
       <c r="D317">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="318">
@@ -6079,7 +6079,7 @@
         <v>6</v>
       </c>
       <c r="D318">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="319">
@@ -6547,7 +6547,7 @@
         <v>6</v>
       </c>
       <c r="D344">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="345">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C348">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C358">
@@ -7105,7 +7105,7 @@
         <v>59</v>
       </c>
       <c r="D375">
-        <v>0.0009440151042416679</v>
+        <v>0.000944015104241668</v>
       </c>
     </row>
     <row r="376">
@@ -8401,7 +8401,7 @@
         <v>59</v>
       </c>
       <c r="D447">
-        <v>0.0009440151042416679</v>
+        <v>0.000944015104241668</v>
       </c>
     </row>
     <row r="448">
@@ -9067,7 +9067,7 @@
         <v>6</v>
       </c>
       <c r="D484">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="485">
@@ -9661,7 +9661,7 @@
         <v>6</v>
       </c>
       <c r="D517">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="518">
@@ -9949,7 +9949,7 @@
         <v>6</v>
       </c>
       <c r="D533">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="534">
@@ -10291,7 +10291,7 @@
         <v>6</v>
       </c>
       <c r="D552">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="553">
@@ -10849,7 +10849,7 @@
         <v>6</v>
       </c>
       <c r="D583">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="584">
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="D588">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="589">
@@ -10957,7 +10957,7 @@
         <v>6</v>
       </c>
       <c r="D589">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="590">
@@ -12577,7 +12577,7 @@
         <v>6</v>
       </c>
       <c r="D679">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="680">
@@ -12937,7 +12937,7 @@
         <v>57</v>
       </c>
       <c r="D699">
-        <v>0.0009120145922334757</v>
+        <v>0.0009120145922334756</v>
       </c>
     </row>
     <row r="700">
@@ -14269,7 +14269,7 @@
         <v>57</v>
       </c>
       <c r="D773">
-        <v>0.0009120145922334757</v>
+        <v>0.0009120145922334756</v>
       </c>
     </row>
     <row r="774">
@@ -15025,7 +15025,7 @@
         <v>6</v>
       </c>
       <c r="D815">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="816">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C830">
@@ -15403,7 +15403,7 @@
         <v>6</v>
       </c>
       <c r="D836">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="837">
@@ -16303,7 +16303,7 @@
         <v>6</v>
       </c>
       <c r="D886">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="887">
@@ -16465,7 +16465,7 @@
         <v>6</v>
       </c>
       <c r="D895">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="896">
@@ -17653,7 +17653,7 @@
         <v>6</v>
       </c>
       <c r="D961">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="962">
@@ -17959,7 +17959,7 @@
         <v>6</v>
       </c>
       <c r="D978">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="979">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C981">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C982">
@@ -18535,7 +18535,7 @@
         <v>6</v>
       </c>
       <c r="D1010">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1011">
@@ -18913,7 +18913,7 @@
         <v>6</v>
       </c>
       <c r="D1031">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1032">
@@ -19003,7 +19003,7 @@
         <v>6</v>
       </c>
       <c r="D1036">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1037">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1042">
@@ -19201,7 +19201,7 @@
         <v>6</v>
       </c>
       <c r="D1047">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1048">
@@ -19471,7 +19471,7 @@
         <v>6</v>
       </c>
       <c r="D1062">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1063">
@@ -20191,7 +20191,7 @@
         <v>6</v>
       </c>
       <c r="D1102">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1103">
@@ -20371,7 +20371,7 @@
         <v>6</v>
       </c>
       <c r="D1112">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1113">
@@ -20983,7 +20983,7 @@
         <v>6</v>
       </c>
       <c r="D1146">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1147">
@@ -21163,7 +21163,7 @@
         <v>60</v>
       </c>
       <c r="D1156">
-        <v>0.0009600153602457639</v>
+        <v>0.000960015360245764</v>
       </c>
     </row>
     <row r="1157">
@@ -21487,7 +21487,7 @@
         <v>6</v>
       </c>
       <c r="D1174">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1175">
@@ -21793,7 +21793,7 @@
         <v>6</v>
       </c>
       <c r="D1191">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1192">
@@ -21919,7 +21919,7 @@
         <v>59</v>
       </c>
       <c r="D1198">
-        <v>0.0009440151042416679</v>
+        <v>0.000944015104241668</v>
       </c>
     </row>
     <row r="1199">
@@ -22009,7 +22009,7 @@
         <v>6</v>
       </c>
       <c r="D1203">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1204">
@@ -22117,7 +22117,7 @@
         <v>6</v>
       </c>
       <c r="D1209">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1210">
@@ -22243,7 +22243,7 @@
         <v>6</v>
       </c>
       <c r="D1216">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1217">
@@ -22801,7 +22801,7 @@
         <v>6</v>
       </c>
       <c r="D1247">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1248">
@@ -22819,7 +22819,7 @@
         <v>6</v>
       </c>
       <c r="D1248">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1249">
@@ -22981,7 +22981,7 @@
         <v>6</v>
       </c>
       <c r="D1257">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1258">
@@ -23953,7 +23953,7 @@
         <v>6</v>
       </c>
       <c r="D1311">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1312">
@@ -24025,7 +24025,7 @@
         <v>60</v>
       </c>
       <c r="D1315">
-        <v>0.0009600153602457639</v>
+        <v>0.000960015360245764</v>
       </c>
     </row>
     <row r="1316">
@@ -24727,7 +24727,7 @@
         <v>6</v>
       </c>
       <c r="D1354">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1355">
@@ -25051,7 +25051,7 @@
         <v>6</v>
       </c>
       <c r="D1372">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1373">
@@ -25555,7 +25555,7 @@
         <v>6</v>
       </c>
       <c r="D1400">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1401">
@@ -25573,7 +25573,7 @@
         <v>6</v>
       </c>
       <c r="D1401">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1402">
@@ -25663,7 +25663,7 @@
         <v>6</v>
       </c>
       <c r="D1406">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1407">
@@ -25735,7 +25735,7 @@
         <v>6</v>
       </c>
       <c r="D1410">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1411">
@@ -26095,7 +26095,7 @@
         <v>6</v>
       </c>
       <c r="D1430">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1431">
@@ -26527,7 +26527,7 @@
         <v>6</v>
       </c>
       <c r="D1454">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1455">
@@ -27355,7 +27355,7 @@
         <v>6</v>
       </c>
       <c r="D1500">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1501">
@@ -27625,7 +27625,7 @@
         <v>6</v>
       </c>
       <c r="D1515">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1516">
@@ -27841,7 +27841,7 @@
         <v>6</v>
       </c>
       <c r="D1527">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1528">
@@ -28039,7 +28039,7 @@
         <v>60</v>
       </c>
       <c r="D1538">
-        <v>0.0009600153602457639</v>
+        <v>0.000960015360245764</v>
       </c>
     </row>
     <row r="1539">
@@ -28183,7 +28183,7 @@
         <v>6</v>
       </c>
       <c r="D1546">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1547">
@@ -28212,7 +28212,7 @@
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1548">
@@ -28453,7 +28453,7 @@
         <v>6</v>
       </c>
       <c r="D1561">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1562">
@@ -28795,7 +28795,7 @@
         <v>6</v>
       </c>
       <c r="D1580">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1581">
@@ -28903,7 +28903,7 @@
         <v>6</v>
       </c>
       <c r="D1586">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1587">
@@ -29641,7 +29641,7 @@
         <v>6</v>
       </c>
       <c r="D1627">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1628">
@@ -29965,7 +29965,7 @@
         <v>6</v>
       </c>
       <c r="D1645">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1646">
@@ -30757,7 +30757,7 @@
         <v>6</v>
       </c>
       <c r="D1689">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1690">
@@ -32053,7 +32053,7 @@
         <v>6</v>
       </c>
       <c r="D1761">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1762">
@@ -32575,7 +32575,7 @@
         <v>6</v>
       </c>
       <c r="D1790">
-        <v>9.600153602457639E-05</v>
+        <v>9.60015360245764E-05</v>
       </c>
     </row>
     <row r="1791">
